--- a/data/trending_integrated_20260921_09.xlsx
+++ b/data/trending_integrated_20260921_09.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Z5"/>
+  <dimension ref="A1:Z7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -563,31 +563,31 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>가온전선</t>
+          <t>삼성전자</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>336000</v>
+        <v>269500</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>'+2.75%</t>
+          <t>'+3.26%</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>1.66</v>
+        <v>-0.02</v>
       </c>
       <c r="E2" t="n">
-        <v>51</v>
+        <v>354</v>
       </c>
       <c r="F2" t="n">
-        <v>41</v>
+        <v>239</v>
       </c>
       <c r="G2" t="n">
-        <v>133</v>
+        <v>1558</v>
       </c>
       <c r="H2" t="n">
-        <v>3.62</v>
+        <v>46.46</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
@@ -595,28 +595,28 @@
         </is>
       </c>
       <c r="J2" t="n">
-        <v>327000</v>
+        <v>261000</v>
       </c>
       <c r="K2" t="n">
-        <v>324000</v>
+        <v>264000</v>
       </c>
       <c r="L2" t="n">
-        <v>336500</v>
+        <v>271500</v>
       </c>
       <c r="M2" t="n">
-        <v>322500</v>
+        <v>263500</v>
       </c>
       <c r="N2" t="n">
-        <v>1.96</v>
+        <v>46.48</v>
       </c>
       <c r="O2" t="n">
-        <v>6333399750</v>
+        <v>696285044500</v>
       </c>
       <c r="P2" t="n">
-        <v>635000</v>
+        <v>374500</v>
       </c>
       <c r="Q2" t="n">
-        <v>52600</v>
+        <v>81100</v>
       </c>
       <c r="R2" t="n">
         <v>0</v>
@@ -626,7 +626,7 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>단기 급등 후 쉬어가는 흐름 속 일부 투자자들의 차익 실현 및 관망 심리 존재.</t>
+          <t>AI 감속론 부인하며 내년 상반기까지 상승장 전망. 3분기 배당 관련 긍정적 언급 있으나, 검찰 개혁 등 정치적 내용 포함. 목표가 27만원 언급.</t>
         </is>
       </c>
       <c r="U2" t="inlineStr"/>
@@ -635,11 +635,11 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>['급등', '차익실현', '관망']</t>
+          <t>['AI', '배당', '상승장']</t>
         </is>
       </c>
       <c r="X2" t="n">
-        <v>1</v>
+        <v>110</v>
       </c>
       <c r="Y2" t="inlineStr">
         <is>
@@ -648,7 +648,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>000500</t>
+          <t>005930</t>
         </is>
       </c>
     </row>
@@ -659,24 +659,24 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>30200</v>
+        <v>29850</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>'+1.85%</t>
+          <t>'+0.67%</t>
         </is>
       </c>
       <c r="D3" t="n">
         <v>-0.48</v>
       </c>
       <c r="E3" t="n">
-        <v>61</v>
+        <v>73</v>
       </c>
       <c r="F3" t="n">
-        <v>51</v>
+        <v>58</v>
       </c>
       <c r="G3" t="n">
-        <v>458</v>
+        <v>491</v>
       </c>
       <c r="H3" t="n">
         <v>16.67</v>
@@ -696,13 +696,13 @@
         <v>30400</v>
       </c>
       <c r="M3" t="n">
-        <v>30050</v>
+        <v>29400</v>
       </c>
       <c r="N3" t="n">
         <v>17.15</v>
       </c>
       <c r="O3" t="n">
-        <v>662658550</v>
+        <v>2193021675</v>
       </c>
       <c r="P3" t="n">
         <v>69200</v>
@@ -718,7 +718,7 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>FDA 승인 기대감 속 주가 등락 반복, 투자자들의 신중론과 급락 가능성 경고.</t>
+          <t>FDA 승인 관련 기대감과 함께 과거 패턴 반복에 대한 우려 제기. 투자자 손실 언급하며 탈출 기회 강조. 승인 여부에 대한 불확실성 내포.</t>
         </is>
       </c>
       <c r="U3" t="inlineStr"/>
@@ -727,7 +727,7 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>['FDA', '승인', '주가']</t>
+          <t>['FDA', '승인', '손실']</t>
         </is>
       </c>
       <c r="X3" t="n">
@@ -751,24 +751,24 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1873000</v>
+        <v>1856000</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>'+0.86%</t>
+          <t>'-0.05%</t>
         </is>
       </c>
       <c r="D4" t="n">
         <v>0.13</v>
       </c>
       <c r="E4" t="n">
-        <v>366</v>
+        <v>406</v>
       </c>
       <c r="F4" t="n">
-        <v>243</v>
+        <v>263</v>
       </c>
       <c r="G4" t="n">
-        <v>1872</v>
+        <v>1948</v>
       </c>
       <c r="H4" t="n">
         <v>50.23</v>
@@ -785,16 +785,16 @@
         <v>1872000</v>
       </c>
       <c r="L4" t="n">
-        <v>1875000</v>
+        <v>1888000</v>
       </c>
       <c r="M4" t="n">
-        <v>1863000</v>
+        <v>1856000</v>
       </c>
       <c r="N4" t="n">
         <v>50.1</v>
       </c>
       <c r="O4" t="n">
-        <v>183788246500</v>
+        <v>560977853500</v>
       </c>
       <c r="P4" t="n">
         <v>2987000</v>
@@ -843,24 +843,24 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>18240</v>
+        <v>18080</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>'-0.44%</t>
+          <t>'-1.31%</t>
         </is>
       </c>
       <c r="D5" t="n">
         <v>3.29</v>
       </c>
       <c r="E5" t="n">
-        <v>48</v>
+        <v>64</v>
       </c>
       <c r="F5" t="n">
-        <v>36</v>
+        <v>47</v>
       </c>
       <c r="G5" t="n">
-        <v>368</v>
+        <v>404</v>
       </c>
       <c r="H5" t="n">
         <v>7.9</v>
@@ -886,7 +886,7 @@
         <v>4.61</v>
       </c>
       <c r="O5" t="n">
-        <v>22295537440</v>
+        <v>61607454275</v>
       </c>
       <c r="P5" t="n">
         <v>31500</v>
@@ -902,16 +902,16 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>미국 광통신 AI 주 강세 및 국내외 수주량 증가 기대감, 기관 매수세 유입으로 인한 상승 전망.</t>
+          <t>미국 광통신 AI 주 강세 및 국내 관련주 상승 언급. 기관의 최근 매수세와 추천에 대한 긍정적 전망 제시. 투자 주의 및 외인 매도 가능성 언급.</t>
         </is>
       </c>
       <c r="U5" t="inlineStr"/>
       <c r="V5" t="n">
-        <v>0.4</v>
+        <v>0.3</v>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>['광통신', 'AI', '수주']</t>
+          <t>['광통신', 'AI', '기관']</t>
         </is>
       </c>
       <c r="X5" t="n">
@@ -925,6 +925,190 @@
       <c r="Z5" t="inlineStr">
         <is>
           <t>010170</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>한화시스템</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>78800</v>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>'-1.50%</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>-0.1</v>
+      </c>
+      <c r="E6" t="n">
+        <v>43</v>
+      </c>
+      <c r="F6" t="n">
+        <v>32</v>
+      </c>
+      <c r="G6" t="n">
+        <v>237</v>
+      </c>
+      <c r="H6" t="n">
+        <v>10.58</v>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>MarketType.KOSPI</t>
+        </is>
+      </c>
+      <c r="J6" t="n">
+        <v>80000</v>
+      </c>
+      <c r="K6" t="n">
+        <v>82900</v>
+      </c>
+      <c r="L6" t="n">
+        <v>83000</v>
+      </c>
+      <c r="M6" t="n">
+        <v>78100</v>
+      </c>
+      <c r="N6" t="n">
+        <v>10.68</v>
+      </c>
+      <c r="O6" t="n">
+        <v>27122926300</v>
+      </c>
+      <c r="P6" t="n">
+        <v>184000</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>44750</v>
+      </c>
+      <c r="R6" t="n">
+        <v>0</v>
+      </c>
+      <c r="S6" t="n">
+        <v>0</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>K-방산 관련 긍정적 뉴스 인용하며 주가 상승 기대. 공매도 세력에 대한 부정적 언급과 10만원대 복귀 희망.</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr"/>
+      <c r="V6" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>['K-방산', '드론', '공매도']</t>
+        </is>
+      </c>
+      <c r="X6" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>활성</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>272210</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>가온전선</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>319500</v>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>'-2.29%</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="E7" t="n">
+        <v>55</v>
+      </c>
+      <c r="F7" t="n">
+        <v>42</v>
+      </c>
+      <c r="G7" t="n">
+        <v>135</v>
+      </c>
+      <c r="H7" t="n">
+        <v>3.62</v>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>MarketType.KOSPI</t>
+        </is>
+      </c>
+      <c r="J7" t="n">
+        <v>327000</v>
+      </c>
+      <c r="K7" t="n">
+        <v>324000</v>
+      </c>
+      <c r="L7" t="n">
+        <v>340500</v>
+      </c>
+      <c r="M7" t="n">
+        <v>318500</v>
+      </c>
+      <c r="N7" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="O7" t="n">
+        <v>31101860250</v>
+      </c>
+      <c r="P7" t="n">
+        <v>635000</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>52600</v>
+      </c>
+      <c r="R7" t="n">
+        <v>0</v>
+      </c>
+      <c r="S7" t="n">
+        <v>0</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>주가 상승에 대한 기대감과 40만원 돌파 전망. 회장님 따님 수익 언급. 그러나 고평가 논란 및 차익 실현 가능성 언급.</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr"/>
+      <c r="V7" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>['고평가', '수익', '차익실현']</t>
+        </is>
+      </c>
+      <c r="X7" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>활성</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>000500</t>
         </is>
       </c>
     </row>

--- a/data/trending_integrated_20260921_09.xlsx
+++ b/data/trending_integrated_20260921_09.xlsx
@@ -567,24 +567,24 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>269500</v>
+        <v>268500</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>'+3.26%</t>
+          <t>'+2.87%</t>
         </is>
       </c>
       <c r="D2" t="n">
         <v>-0.02</v>
       </c>
       <c r="E2" t="n">
-        <v>354</v>
+        <v>415</v>
       </c>
       <c r="F2" t="n">
-        <v>239</v>
+        <v>274</v>
       </c>
       <c r="G2" t="n">
-        <v>1558</v>
+        <v>1748</v>
       </c>
       <c r="H2" t="n">
         <v>46.46</v>
@@ -610,7 +610,7 @@
         <v>46.48</v>
       </c>
       <c r="O2" t="n">
-        <v>696285044500</v>
+        <v>981779751500</v>
       </c>
       <c r="P2" t="n">
         <v>374500</v>
@@ -626,16 +626,16 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>AI 감속론 부인하며 내년 상반기까지 상승장 전망. 3분기 배당 관련 긍정적 언급 있으나, 검찰 개혁 등 정치적 내용 포함. 목표가 27만원 언급.</t>
+          <t>삼성전자, 3분기 배당 예정 및 AI 관련 긍정적 전망. 다만, 정치적 언급과 증권사 시스템 문제 제기.</t>
         </is>
       </c>
       <c r="U2" t="inlineStr"/>
       <c r="V2" t="n">
-        <v>0.2</v>
+        <v>0.1</v>
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>['AI', '배당', '상승장']</t>
+          <t>['배당', 'AI', '전망']</t>
         </is>
       </c>
       <c r="X2" t="n">
@@ -659,24 +659,24 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>29850</v>
+        <v>30000</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>'+0.67%</t>
+          <t>'+1.18%</t>
         </is>
       </c>
       <c r="D3" t="n">
         <v>-0.48</v>
       </c>
       <c r="E3" t="n">
-        <v>73</v>
+        <v>78</v>
       </c>
       <c r="F3" t="n">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="G3" t="n">
-        <v>491</v>
+        <v>558</v>
       </c>
       <c r="H3" t="n">
         <v>16.67</v>
@@ -702,7 +702,7 @@
         <v>17.15</v>
       </c>
       <c r="O3" t="n">
-        <v>2193021675</v>
+        <v>2704845800</v>
       </c>
       <c r="P3" t="n">
         <v>69200</v>
@@ -718,16 +718,16 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>FDA 승인 관련 기대감과 함께 과거 패턴 반복에 대한 우려 제기. 투자자 손실 언급하며 탈출 기회 강조. 승인 여부에 대한 불확실성 내포.</t>
+          <t>HLB, FDA 승인 관련 기대감과 실패 가능성 혼재. 기관 및 외인 매도세 발생.</t>
         </is>
       </c>
       <c r="U3" t="inlineStr"/>
       <c r="V3" t="n">
-        <v>0.3</v>
+        <v>0.2</v>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>['FDA', '승인', '손실']</t>
+          <t>['FDA 승인', '담관암', '매도세']</t>
         </is>
       </c>
       <c r="X3" t="n">
@@ -751,24 +751,24 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1856000</v>
+        <v>1854000</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>'-0.05%</t>
+          <t>'-0.16%</t>
         </is>
       </c>
       <c r="D4" t="n">
         <v>0.13</v>
       </c>
       <c r="E4" t="n">
-        <v>406</v>
+        <v>486</v>
       </c>
       <c r="F4" t="n">
-        <v>263</v>
+        <v>303</v>
       </c>
       <c r="G4" t="n">
-        <v>1948</v>
+        <v>2098</v>
       </c>
       <c r="H4" t="n">
         <v>50.23</v>
@@ -788,13 +788,13 @@
         <v>1888000</v>
       </c>
       <c r="M4" t="n">
-        <v>1856000</v>
+        <v>1847000</v>
       </c>
       <c r="N4" t="n">
         <v>50.1</v>
       </c>
       <c r="O4" t="n">
-        <v>560977853500</v>
+        <v>842753224000</v>
       </c>
       <c r="P4" t="n">
         <v>2987000</v>
@@ -843,24 +843,24 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>18080</v>
+        <v>17955</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>'-1.31%</t>
+          <t>'-1.99%</t>
         </is>
       </c>
       <c r="D5" t="n">
         <v>3.29</v>
       </c>
       <c r="E5" t="n">
-        <v>64</v>
+        <v>83</v>
       </c>
       <c r="F5" t="n">
-        <v>47</v>
+        <v>62</v>
       </c>
       <c r="G5" t="n">
-        <v>404</v>
+        <v>463</v>
       </c>
       <c r="H5" t="n">
         <v>7.9</v>
@@ -880,13 +880,13 @@
         <v>18590</v>
       </c>
       <c r="M5" t="n">
-        <v>18010</v>
+        <v>17700</v>
       </c>
       <c r="N5" t="n">
         <v>4.61</v>
       </c>
       <c r="O5" t="n">
-        <v>61607454275</v>
+        <v>91670137810</v>
       </c>
       <c r="P5" t="n">
         <v>31500</v>
@@ -902,7 +902,7 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>미국 광통신 AI 주 강세 및 국내 관련주 상승 언급. 기관의 최근 매수세와 추천에 대한 긍정적 전망 제시. 투자 주의 및 외인 매도 가능성 언급.</t>
+          <t>대한광통신, 미국 광통신주 급등 및 기관 매수세 유입으로 인한 긍정적 주가 전망. 다만, 투자 주의 언급.</t>
         </is>
       </c>
       <c r="U5" t="inlineStr"/>
@@ -911,7 +911,7 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>['광통신', 'AI', '기관']</t>
+          <t>['광통신', '기관 매수', '수출']</t>
         </is>
       </c>
       <c r="X5" t="n">
@@ -935,24 +935,24 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>78800</v>
+        <v>78000</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>'-1.50%</t>
+          <t>'-2.50%</t>
         </is>
       </c>
       <c r="D6" t="n">
         <v>-0.1</v>
       </c>
       <c r="E6" t="n">
-        <v>43</v>
+        <v>54</v>
       </c>
       <c r="F6" t="n">
-        <v>32</v>
+        <v>37</v>
       </c>
       <c r="G6" t="n">
-        <v>237</v>
+        <v>260</v>
       </c>
       <c r="H6" t="n">
         <v>10.58</v>
@@ -972,13 +972,13 @@
         <v>83000</v>
       </c>
       <c r="M6" t="n">
-        <v>78100</v>
+        <v>77800</v>
       </c>
       <c r="N6" t="n">
         <v>10.68</v>
       </c>
       <c r="O6" t="n">
-        <v>27122926300</v>
+        <v>34472105800</v>
       </c>
       <c r="P6" t="n">
         <v>184000</v>
@@ -994,16 +994,16 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>K-방산 관련 긍정적 뉴스 인용하며 주가 상승 기대. 공매도 세력에 대한 부정적 언급과 10만원대 복귀 희망.</t>
+          <t>한화시스템, K-방산 관련 유럽 드론 시장 진출 및 매각 이슈. 긍정적 뉴스 기반 상승 기대.</t>
         </is>
       </c>
       <c r="U6" t="inlineStr"/>
       <c r="V6" t="n">
-        <v>0.4</v>
+        <v>0.3</v>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>['K-방산', '드론', '공매도']</t>
+          <t>['K-방산', '드론', '매각']</t>
         </is>
       </c>
       <c r="X6" t="n">
@@ -1027,24 +1027,24 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>319500</v>
+        <v>318000</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>'-2.29%</t>
+          <t>'-2.75%</t>
         </is>
       </c>
       <c r="D7" t="n">
         <v>1.66</v>
       </c>
       <c r="E7" t="n">
-        <v>55</v>
+        <v>62</v>
       </c>
       <c r="F7" t="n">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="G7" t="n">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="H7" t="n">
         <v>3.62</v>
@@ -1064,13 +1064,13 @@
         <v>340500</v>
       </c>
       <c r="M7" t="n">
-        <v>318500</v>
+        <v>315500</v>
       </c>
       <c r="N7" t="n">
         <v>1.96</v>
       </c>
       <c r="O7" t="n">
-        <v>31101860250</v>
+        <v>39803545000</v>
       </c>
       <c r="P7" t="n">
         <v>635000</v>

--- a/data/trending_integrated_20260921_09.xlsx
+++ b/data/trending_integrated_20260921_09.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Z7"/>
+  <dimension ref="A1:Z9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -567,24 +567,24 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>268500</v>
+        <v>270000</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>'+2.87%</t>
+          <t>'+3.45%</t>
         </is>
       </c>
       <c r="D2" t="n">
         <v>-0.02</v>
       </c>
       <c r="E2" t="n">
-        <v>415</v>
+        <v>472</v>
       </c>
       <c r="F2" t="n">
-        <v>274</v>
+        <v>312</v>
       </c>
       <c r="G2" t="n">
-        <v>1748</v>
+        <v>1939</v>
       </c>
       <c r="H2" t="n">
         <v>46.46</v>
@@ -610,7 +610,7 @@
         <v>46.48</v>
       </c>
       <c r="O2" t="n">
-        <v>981779751500</v>
+        <v>1264633677750</v>
       </c>
       <c r="P2" t="n">
         <v>374500</v>
@@ -619,14 +619,14 @@
         <v>81100</v>
       </c>
       <c r="R2" t="n">
-        <v>0</v>
+        <v>1280000</v>
       </c>
       <c r="S2" t="n">
         <v>0</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>삼성전자, 3분기 배당 예정 및 AI 관련 긍정적 전망. 다만, 정치적 언급과 증권사 시스템 문제 제기.</t>
+          <t>AI 감속론 부인, 배당 기대감 속 28만원 안착 전망. 그러나 신한증권 시스템 오류 관련 불만 제기.</t>
         </is>
       </c>
       <c r="U2" t="inlineStr"/>
@@ -635,7 +635,7 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>['배당', 'AI', '전망']</t>
+          <t>['AI', '배당', '전망']</t>
         </is>
       </c>
       <c r="X2" t="n">
@@ -659,24 +659,24 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>30000</v>
+        <v>30100</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>'+1.18%</t>
+          <t>'+1.52%</t>
         </is>
       </c>
       <c r="D3" t="n">
         <v>-0.48</v>
       </c>
       <c r="E3" t="n">
-        <v>78</v>
+        <v>83</v>
       </c>
       <c r="F3" t="n">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="G3" t="n">
-        <v>558</v>
+        <v>596</v>
       </c>
       <c r="H3" t="n">
         <v>16.67</v>
@@ -702,7 +702,7 @@
         <v>17.15</v>
       </c>
       <c r="O3" t="n">
-        <v>2704845800</v>
+        <v>3221690125</v>
       </c>
       <c r="P3" t="n">
         <v>69200</v>
@@ -711,23 +711,23 @@
         <v>24150</v>
       </c>
       <c r="R3" t="n">
-        <v>0</v>
+        <v>-16000</v>
       </c>
       <c r="S3" t="n">
         <v>0</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>HLB, FDA 승인 관련 기대감과 실패 가능성 혼재. 기관 및 외인 매도세 발생.</t>
+          <t>FDA 승인 관련 불확실성 지속, 담관암 임상 결과 및 과거 패턴 반복에 대한 우려 제기. 투자 주의 경고.</t>
         </is>
       </c>
       <c r="U3" t="inlineStr"/>
       <c r="V3" t="n">
-        <v>0.2</v>
+        <v>0.1</v>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>['FDA 승인', '담관암', '매도세']</t>
+          <t>['FDA', '승인', '임상']</t>
         </is>
       </c>
       <c r="X3" t="n">
@@ -751,24 +751,24 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1854000</v>
+        <v>1864000</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>'-0.16%</t>
+          <t>'+0.38%</t>
         </is>
       </c>
       <c r="D4" t="n">
         <v>0.13</v>
       </c>
       <c r="E4" t="n">
-        <v>486</v>
+        <v>548</v>
       </c>
       <c r="F4" t="n">
-        <v>303</v>
+        <v>340</v>
       </c>
       <c r="G4" t="n">
-        <v>2098</v>
+        <v>2263</v>
       </c>
       <c r="H4" t="n">
         <v>50.23</v>
@@ -794,7 +794,7 @@
         <v>50.1</v>
       </c>
       <c r="O4" t="n">
-        <v>842753224000</v>
+        <v>1040237052000</v>
       </c>
       <c r="P4" t="n">
         <v>2987000</v>
@@ -803,7 +803,7 @@
         <v>333000</v>
       </c>
       <c r="R4" t="n">
-        <v>0</v>
+        <v>-60000</v>
       </c>
       <c r="S4" t="n">
         <v>0</v>
@@ -839,83 +839,83 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>대한광통신</t>
+          <t>한화시스템</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>17955</v>
+        <v>77700</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>'-1.99%</t>
+          <t>'-2.88%</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>3.29</v>
+        <v>-0.1</v>
       </c>
       <c r="E5" t="n">
-        <v>83</v>
+        <v>63</v>
       </c>
       <c r="F5" t="n">
-        <v>62</v>
+        <v>44</v>
       </c>
       <c r="G5" t="n">
-        <v>463</v>
+        <v>281</v>
       </c>
       <c r="H5" t="n">
-        <v>7.9</v>
+        <v>10.58</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J5" t="n">
-        <v>18320</v>
+        <v>80000</v>
       </c>
       <c r="K5" t="n">
-        <v>18450</v>
+        <v>82900</v>
       </c>
       <c r="L5" t="n">
-        <v>18590</v>
+        <v>83000</v>
       </c>
       <c r="M5" t="n">
-        <v>17700</v>
+        <v>77500</v>
       </c>
       <c r="N5" t="n">
-        <v>4.61</v>
+        <v>10.68</v>
       </c>
       <c r="O5" t="n">
-        <v>91670137810</v>
+        <v>42699218800</v>
       </c>
       <c r="P5" t="n">
-        <v>31500</v>
+        <v>184000</v>
       </c>
       <c r="Q5" t="n">
-        <v>1272</v>
+        <v>44750</v>
       </c>
       <c r="R5" t="n">
-        <v>0</v>
+        <v>-260000</v>
       </c>
       <c r="S5" t="n">
         <v>0</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>대한광통신, 미국 광통신주 급등 및 기관 매수세 유입으로 인한 긍정적 주가 전망. 다만, 투자 주의 언급.</t>
+          <t>K-방산, 드론 시장 진출 기대감 속 매물대 돌파 시 9만원대 상승 전망. 공매도 청산 및 정부 정책 기대.</t>
         </is>
       </c>
       <c r="U5" t="inlineStr"/>
       <c r="V5" t="n">
-        <v>0.3</v>
+        <v>0.15</v>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>['광통신', '기관 매수', '수출']</t>
+          <t>['K-방산', '드론', '매물대']</t>
         </is>
       </c>
       <c r="X5" t="n">
-        <v>19</v>
+        <v>1</v>
       </c>
       <c r="Y5" t="inlineStr">
         <is>
@@ -924,38 +924,38 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>010170</t>
+          <t>272210</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>한화시스템</t>
+          <t>가온전선</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>78000</v>
+        <v>317500</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>'-2.50%</t>
+          <t>'-2.91%</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>-0.1</v>
+        <v>1.66</v>
       </c>
       <c r="E6" t="n">
-        <v>54</v>
+        <v>65</v>
       </c>
       <c r="F6" t="n">
-        <v>37</v>
+        <v>47</v>
       </c>
       <c r="G6" t="n">
-        <v>260</v>
+        <v>131</v>
       </c>
       <c r="H6" t="n">
-        <v>10.58</v>
+        <v>3.62</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
@@ -963,47 +963,47 @@
         </is>
       </c>
       <c r="J6" t="n">
-        <v>80000</v>
+        <v>327000</v>
       </c>
       <c r="K6" t="n">
-        <v>82900</v>
+        <v>324000</v>
       </c>
       <c r="L6" t="n">
-        <v>83000</v>
+        <v>340500</v>
       </c>
       <c r="M6" t="n">
-        <v>77800</v>
+        <v>315500</v>
       </c>
       <c r="N6" t="n">
-        <v>10.68</v>
+        <v>1.96</v>
       </c>
       <c r="O6" t="n">
-        <v>34472105800</v>
+        <v>43066584250</v>
       </c>
       <c r="P6" t="n">
-        <v>184000</v>
+        <v>635000</v>
       </c>
       <c r="Q6" t="n">
-        <v>44750</v>
+        <v>52600</v>
       </c>
       <c r="R6" t="n">
-        <v>0</v>
+        <v>-23000</v>
       </c>
       <c r="S6" t="n">
         <v>0</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>한화시스템, K-방산 관련 유럽 드론 시장 진출 및 매각 이슈. 긍정적 뉴스 기반 상승 기대.</t>
+          <t>최고가 갱신 기대감 속, 단기 급등 후 차익실현 매물 출회 가능성 및 외국인 수급 변동성 주의.</t>
         </is>
       </c>
       <c r="U6" t="inlineStr"/>
       <c r="V6" t="n">
-        <v>0.3</v>
+        <v>0.05</v>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>['K-방산', '드론', '매각']</t>
+          <t>['단기 급등', '외국인', '차익실현']</t>
         </is>
       </c>
       <c r="X6" t="n">
@@ -1016,99 +1016,283 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>272210</t>
+          <t>000500</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>가온전선</t>
+          <t>대한광통신</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>318000</v>
+        <v>17720</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>'-2.75%</t>
+          <t>'-3.28%</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>1.66</v>
+        <v>3.29</v>
       </c>
       <c r="E7" t="n">
-        <v>62</v>
+        <v>98</v>
       </c>
       <c r="F7" t="n">
-        <v>44</v>
+        <v>75</v>
       </c>
       <c r="G7" t="n">
-        <v>137</v>
+        <v>512</v>
       </c>
       <c r="H7" t="n">
-        <v>3.62</v>
+        <v>7.9</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J7" t="n">
-        <v>327000</v>
+        <v>18320</v>
       </c>
       <c r="K7" t="n">
-        <v>324000</v>
+        <v>18450</v>
       </c>
       <c r="L7" t="n">
-        <v>340500</v>
+        <v>18590</v>
       </c>
       <c r="M7" t="n">
-        <v>315500</v>
+        <v>17700</v>
       </c>
       <c r="N7" t="n">
-        <v>1.96</v>
+        <v>4.61</v>
       </c>
       <c r="O7" t="n">
-        <v>39803545000</v>
+        <v>104543993765</v>
       </c>
       <c r="P7" t="n">
-        <v>635000</v>
+        <v>31500</v>
       </c>
       <c r="Q7" t="n">
-        <v>52600</v>
+        <v>1272</v>
       </c>
       <c r="R7" t="n">
-        <v>0</v>
+        <v>-762000</v>
       </c>
       <c r="S7" t="n">
         <v>0</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>주가 상승에 대한 기대감과 40만원 돌파 전망. 회장님 따님 수익 언급. 그러나 고평가 논란 및 차익 실현 가능성 언급.</t>
+          <t>미국 광통신 AI주 급등 영향, 기관 매수세 유입 및 연말까지 상승 전망. 다만, 외인 매도세 주의 필요.</t>
         </is>
       </c>
       <c r="U7" t="inlineStr"/>
       <c r="V7" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>['광통신', 'AI', '기관']</t>
+        </is>
+      </c>
+      <c r="X7" t="n">
+        <v>19</v>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>활성</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>010170</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>대한전선</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>30300</v>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>'-3.66%</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>0.48</v>
+      </c>
+      <c r="E8" t="n">
+        <v>43</v>
+      </c>
+      <c r="F8" t="n">
+        <v>28</v>
+      </c>
+      <c r="G8" t="n">
+        <v>79</v>
+      </c>
+      <c r="H8" t="n">
+        <v>11.92</v>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>MarketType.KOSPI</t>
+        </is>
+      </c>
+      <c r="J8" t="n">
+        <v>31450</v>
+      </c>
+      <c r="K8" t="n">
+        <v>31500</v>
+      </c>
+      <c r="L8" t="n">
+        <v>31550</v>
+      </c>
+      <c r="M8" t="n">
+        <v>30100</v>
+      </c>
+      <c r="N8" t="n">
+        <v>11.44</v>
+      </c>
+      <c r="O8" t="n">
+        <v>35138784150</v>
+      </c>
+      <c r="P8" t="n">
+        <v>75900</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>15000</v>
+      </c>
+      <c r="R8" t="n">
+        <v>-117000</v>
+      </c>
+      <c r="S8" t="n">
+        <v>0</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>오늘 상승 기대감 속, 전선주 전반의 약세 및 주가 하락세가 관찰됨.</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr"/>
+      <c r="V8" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>['전선주', '수급', '하락']</t>
+        </is>
+      </c>
+      <c r="X8" t="n">
+        <v>2</v>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>활성</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>001440</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>오름테라퓨틱</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>26850</v>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>'-28.21%</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="E9" t="n">
+        <v>344</v>
+      </c>
+      <c r="F9" t="n">
+        <v>213</v>
+      </c>
+      <c r="G9" t="n">
+        <v>702</v>
+      </c>
+      <c r="H9" t="n">
+        <v>7.09</v>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>MarketType.KOSDAQ</t>
+        </is>
+      </c>
+      <c r="J9" t="n">
+        <v>37400</v>
+      </c>
+      <c r="K9" t="n">
+        <v>26450</v>
+      </c>
+      <c r="L9" t="n">
+        <v>27300</v>
+      </c>
+      <c r="M9" t="n">
+        <v>26200</v>
+      </c>
+      <c r="N9" t="n">
+        <v>7.08</v>
+      </c>
+      <c r="O9" t="n">
+        <v>38457487475</v>
+      </c>
+      <c r="P9" t="n">
+        <v>146600</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>26200</v>
+      </c>
+      <c r="R9" t="n">
+        <v>8000</v>
+      </c>
+      <c r="S9" t="n">
+        <v>0</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>하한가 기록 후 반등 시도하나, 임상 결과 및 글로벌 제약사 협상 지연으로 인한 불확실성 지속.</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr"/>
+      <c r="V9" t="n">
         <v>0.1</v>
       </c>
-      <c r="W7" t="inlineStr">
-        <is>
-          <t>['고평가', '수익', '차익실현']</t>
-        </is>
-      </c>
-      <c r="X7" t="n">
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>['임상', '바이오', '하한가']</t>
+        </is>
+      </c>
+      <c r="X9" t="n">
         <v>1</v>
       </c>
-      <c r="Y7" t="inlineStr">
+      <c r="Y9" t="inlineStr">
         <is>
           <t>활성</t>
         </is>
       </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>000500</t>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>475830</t>
         </is>
       </c>
     </row>

--- a/data/trending_integrated_20260921_09.xlsx
+++ b/data/trending_integrated_20260921_09.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Z9"/>
+  <dimension ref="A1:Z11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -563,83 +563,83 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>삼성전자</t>
+          <t>스카이랩스</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>270000</v>
+        <v>22550</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>'+3.45%</t>
+          <t>'+16.00%</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>-0.02</v>
+        <v>-0.04</v>
       </c>
       <c r="E2" t="n">
-        <v>472</v>
+        <v>44</v>
       </c>
       <c r="F2" t="n">
-        <v>312</v>
+        <v>39</v>
       </c>
       <c r="G2" t="n">
-        <v>1939</v>
+        <v>73</v>
       </c>
       <c r="H2" t="n">
-        <v>46.46</v>
+        <v>0.35</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J2" t="n">
-        <v>261000</v>
+        <v>19440</v>
       </c>
       <c r="K2" t="n">
-        <v>264000</v>
+        <v>20200</v>
       </c>
       <c r="L2" t="n">
-        <v>271500</v>
+        <v>23150</v>
       </c>
       <c r="M2" t="n">
-        <v>263500</v>
+        <v>19610</v>
       </c>
       <c r="N2" t="n">
-        <v>46.48</v>
+        <v>0.39</v>
       </c>
       <c r="O2" t="n">
-        <v>1264633677750</v>
+        <v>77373063160</v>
       </c>
       <c r="P2" t="n">
-        <v>374500</v>
+        <v>39350</v>
       </c>
       <c r="Q2" t="n">
-        <v>81100</v>
+        <v>8200</v>
       </c>
       <c r="R2" t="n">
-        <v>1280000</v>
+        <v>100000</v>
       </c>
       <c r="S2" t="n">
         <v>0</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>AI 감속론 부인, 배당 기대감 속 28만원 안착 전망. 그러나 신한증권 시스템 오류 관련 불만 제기.</t>
+          <t>美 타임 선정 '세계 최고 헬스테크 기업' 그룹 선정, 글로벌 경쟁력 부각. 주가 급락 후 반등 시도.</t>
         </is>
       </c>
       <c r="U2" t="inlineStr"/>
       <c r="V2" t="n">
-        <v>0.1</v>
+        <v>0.7</v>
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>['AI', '배당', '전망']</t>
+          <t>['헬스테크', '타임지', '바이오']</t>
         </is>
       </c>
       <c r="X2" t="n">
-        <v>110</v>
+        <v>1</v>
       </c>
       <c r="Y2" t="inlineStr">
         <is>
@@ -648,90 +648,90 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>005930</t>
+          <t>386380</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>HLB</t>
+          <t>광전자</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>30100</v>
+        <v>11440</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>'+1.52%</t>
+          <t>'+8.75%</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>-0.48</v>
+        <v>0.16</v>
       </c>
       <c r="E3" t="n">
-        <v>83</v>
+        <v>44</v>
       </c>
       <c r="F3" t="n">
-        <v>64</v>
+        <v>32</v>
       </c>
       <c r="G3" t="n">
-        <v>596</v>
+        <v>103</v>
       </c>
       <c r="H3" t="n">
-        <v>16.67</v>
+        <v>18.29</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J3" t="n">
-        <v>29650</v>
+        <v>10520</v>
       </c>
       <c r="K3" t="n">
-        <v>30400</v>
+        <v>10780</v>
       </c>
       <c r="L3" t="n">
-        <v>30400</v>
+        <v>12190</v>
       </c>
       <c r="M3" t="n">
-        <v>29400</v>
+        <v>10590</v>
       </c>
       <c r="N3" t="n">
-        <v>17.15</v>
+        <v>18.13</v>
       </c>
       <c r="O3" t="n">
-        <v>3221690125</v>
+        <v>132353333595</v>
       </c>
       <c r="P3" t="n">
-        <v>69200</v>
+        <v>22450</v>
       </c>
       <c r="Q3" t="n">
-        <v>24150</v>
+        <v>1760</v>
       </c>
       <c r="R3" t="n">
-        <v>-16000</v>
+        <v>167000</v>
       </c>
       <c r="S3" t="n">
         <v>0</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>FDA 승인 관련 불확실성 지속, 담관암 임상 결과 및 과거 패턴 반복에 대한 우려 제기. 투자 주의 경고.</t>
+          <t>광통신주 및 나스닥 선물 상승 영향, 추격 매수 주의.</t>
         </is>
       </c>
       <c r="U3" t="inlineStr"/>
       <c r="V3" t="n">
-        <v>0.1</v>
+        <v>0.3</v>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>['FDA', '승인', '임상']</t>
+          <t>['광통신', '나스닥', 'RFHIC']</t>
         </is>
       </c>
       <c r="X3" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="Y3" t="inlineStr">
         <is>
@@ -740,38 +740,38 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>028300</t>
+          <t>017900</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>SK하이닉스</t>
+          <t>삼성전자</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1864000</v>
+        <v>269500</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>'+0.38%</t>
+          <t>'+3.26%</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>0.13</v>
+        <v>-0.02</v>
       </c>
       <c r="E4" t="n">
-        <v>548</v>
+        <v>510</v>
       </c>
       <c r="F4" t="n">
-        <v>340</v>
+        <v>338</v>
       </c>
       <c r="G4" t="n">
-        <v>2263</v>
+        <v>2144</v>
       </c>
       <c r="H4" t="n">
-        <v>50.23</v>
+        <v>46.46</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
@@ -779,51 +779,51 @@
         </is>
       </c>
       <c r="J4" t="n">
-        <v>1857000</v>
+        <v>261000</v>
       </c>
       <c r="K4" t="n">
-        <v>1872000</v>
+        <v>264000</v>
       </c>
       <c r="L4" t="n">
-        <v>1888000</v>
+        <v>271500</v>
       </c>
       <c r="M4" t="n">
-        <v>1847000</v>
+        <v>263500</v>
       </c>
       <c r="N4" t="n">
-        <v>50.1</v>
+        <v>46.48</v>
       </c>
       <c r="O4" t="n">
-        <v>1040237052000</v>
+        <v>1402434337250</v>
       </c>
       <c r="P4" t="n">
-        <v>2987000</v>
+        <v>374500</v>
       </c>
       <c r="Q4" t="n">
-        <v>333000</v>
+        <v>81100</v>
       </c>
       <c r="R4" t="n">
-        <v>-60000</v>
+        <v>1280000</v>
       </c>
       <c r="S4" t="n">
         <v>0</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>AI 시장 성장 전망과 HBM 관련 긍정적 뉴스, 반도체 섹터 강세, 외인 매수세 유입에 따른 20만 돌파 기대감 형성.</t>
+          <t>AI 감속론 부인, 배당 기대감 속 목표가 27만원 제시. 신한증권 서버 불안정 문제 발생.</t>
         </is>
       </c>
       <c r="U4" t="inlineStr"/>
       <c r="V4" t="n">
-        <v>0.6</v>
+        <v>0.2</v>
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>['HBM', 'AI', '반도체']</t>
+          <t>['AI', '배당', '목표가']</t>
         </is>
       </c>
       <c r="X4" t="n">
-        <v>75</v>
+        <v>110</v>
       </c>
       <c r="Y4" t="inlineStr">
         <is>
@@ -832,86 +832,86 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>000660</t>
+          <t>005930</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>한화시스템</t>
+          <t>HLB</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>77700</v>
+        <v>30250</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>'-2.88%</t>
+          <t>'+2.02%</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>-0.1</v>
+        <v>-0.48</v>
       </c>
       <c r="E5" t="n">
-        <v>63</v>
+        <v>88</v>
       </c>
       <c r="F5" t="n">
-        <v>44</v>
+        <v>69</v>
       </c>
       <c r="G5" t="n">
-        <v>281</v>
+        <v>613</v>
       </c>
       <c r="H5" t="n">
-        <v>10.58</v>
+        <v>16.67</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J5" t="n">
-        <v>80000</v>
+        <v>29650</v>
       </c>
       <c r="K5" t="n">
-        <v>82900</v>
+        <v>30400</v>
       </c>
       <c r="L5" t="n">
-        <v>83000</v>
+        <v>30400</v>
       </c>
       <c r="M5" t="n">
-        <v>77500</v>
+        <v>29400</v>
       </c>
       <c r="N5" t="n">
-        <v>10.68</v>
+        <v>17.15</v>
       </c>
       <c r="O5" t="n">
-        <v>42699218800</v>
+        <v>3722766750</v>
       </c>
       <c r="P5" t="n">
-        <v>184000</v>
+        <v>69200</v>
       </c>
       <c r="Q5" t="n">
-        <v>44750</v>
+        <v>24150</v>
       </c>
       <c r="R5" t="n">
-        <v>-260000</v>
+        <v>-16000</v>
       </c>
       <c r="S5" t="n">
         <v>0</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>K-방산, 드론 시장 진출 기대감 속 매물대 돌파 시 9만원대 상승 전망. 공매도 청산 및 정부 정책 기대.</t>
+          <t>FDA 승인 관련 불확실성 지속, 담관암 임상 결과 및 과거 패턴 반복에 대한 우려 제기. 투자 주의 경고.</t>
         </is>
       </c>
       <c r="U5" t="inlineStr"/>
       <c r="V5" t="n">
-        <v>0.15</v>
+        <v>0.1</v>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>['K-방산', '드론', '매물대']</t>
+          <t>['FDA', '승인', '임상']</t>
         </is>
       </c>
       <c r="X5" t="n">
@@ -924,38 +924,38 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>272210</t>
+          <t>028300</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>가온전선</t>
+          <t>SK하이닉스</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>317500</v>
+        <v>1859000</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>'-2.91%</t>
+          <t>'+0.11%</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>1.66</v>
+        <v>0.13</v>
       </c>
       <c r="E6" t="n">
-        <v>65</v>
+        <v>586</v>
       </c>
       <c r="F6" t="n">
-        <v>47</v>
+        <v>361</v>
       </c>
       <c r="G6" t="n">
-        <v>131</v>
+        <v>2466</v>
       </c>
       <c r="H6" t="n">
-        <v>3.62</v>
+        <v>50.23</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
@@ -963,51 +963,51 @@
         </is>
       </c>
       <c r="J6" t="n">
-        <v>327000</v>
+        <v>1857000</v>
       </c>
       <c r="K6" t="n">
-        <v>324000</v>
+        <v>1872000</v>
       </c>
       <c r="L6" t="n">
-        <v>340500</v>
+        <v>1888000</v>
       </c>
       <c r="M6" t="n">
-        <v>315500</v>
+        <v>1847000</v>
       </c>
       <c r="N6" t="n">
-        <v>1.96</v>
+        <v>50.1</v>
       </c>
       <c r="O6" t="n">
-        <v>43066584250</v>
+        <v>1141935987500</v>
       </c>
       <c r="P6" t="n">
-        <v>635000</v>
+        <v>2987000</v>
       </c>
       <c r="Q6" t="n">
-        <v>52600</v>
+        <v>333000</v>
       </c>
       <c r="R6" t="n">
-        <v>-23000</v>
+        <v>-60000</v>
       </c>
       <c r="S6" t="n">
         <v>0</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>최고가 갱신 기대감 속, 단기 급등 후 차익실현 매물 출회 가능성 및 외국인 수급 변동성 주의.</t>
+          <t>HBM 수율 문제에도 불구, 반도체 시장 성장 및 수출 호조 전망. 외인 매수세 유입 및 200만닉스 돌파 기대.</t>
         </is>
       </c>
       <c r="U6" t="inlineStr"/>
       <c r="V6" t="n">
-        <v>0.05</v>
+        <v>0.6</v>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>['단기 급등', '외국인', '차익실현']</t>
+          <t>['HBM', '반도체', '수출']</t>
         </is>
       </c>
       <c r="X6" t="n">
-        <v>1</v>
+        <v>75</v>
       </c>
       <c r="Y6" t="inlineStr">
         <is>
@@ -1016,7 +1016,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>000500</t>
+          <t>000660</t>
         </is>
       </c>
     </row>
@@ -1027,24 +1027,24 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>17720</v>
+        <v>17790</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>'-3.28%</t>
+          <t>'-2.89%</t>
         </is>
       </c>
       <c r="D7" t="n">
         <v>3.29</v>
       </c>
       <c r="E7" t="n">
-        <v>98</v>
+        <v>112</v>
       </c>
       <c r="F7" t="n">
-        <v>75</v>
+        <v>83</v>
       </c>
       <c r="G7" t="n">
-        <v>512</v>
+        <v>558</v>
       </c>
       <c r="H7" t="n">
         <v>7.9</v>
@@ -1064,13 +1064,13 @@
         <v>18590</v>
       </c>
       <c r="M7" t="n">
-        <v>17700</v>
+        <v>17590</v>
       </c>
       <c r="N7" t="n">
         <v>4.61</v>
       </c>
       <c r="O7" t="n">
-        <v>104543993765</v>
+        <v>120891809385</v>
       </c>
       <c r="P7" t="n">
         <v>31500</v>
@@ -1086,16 +1086,16 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>미국 광통신 AI주 급등 영향, 기관 매수세 유입 및 연말까지 상승 전망. 다만, 외인 매도세 주의 필요.</t>
+          <t>미국 광통신주 및 나스닥 선물 상승에 따른 긍정적 전망. 기관 매수세 확인 및 연말까지 상승 기대.</t>
         </is>
       </c>
       <c r="U7" t="inlineStr"/>
       <c r="V7" t="n">
-        <v>0.2</v>
+        <v>0.5</v>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>['광통신', 'AI', '기관']</t>
+          <t>['광통신', '나스닥', '기관']</t>
         </is>
       </c>
       <c r="X7" t="n">
@@ -1115,31 +1115,31 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>대한전선</t>
+          <t>가온전선</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>30300</v>
+        <v>313500</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>'-3.66%</t>
+          <t>'-4.13%</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>0.48</v>
+        <v>1.66</v>
       </c>
       <c r="E8" t="n">
-        <v>43</v>
+        <v>69</v>
       </c>
       <c r="F8" t="n">
-        <v>28</v>
+        <v>50</v>
       </c>
       <c r="G8" t="n">
-        <v>79</v>
+        <v>139</v>
       </c>
       <c r="H8" t="n">
-        <v>11.92</v>
+        <v>3.62</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
@@ -1147,51 +1147,51 @@
         </is>
       </c>
       <c r="J8" t="n">
-        <v>31450</v>
+        <v>327000</v>
       </c>
       <c r="K8" t="n">
-        <v>31500</v>
+        <v>324000</v>
       </c>
       <c r="L8" t="n">
-        <v>31550</v>
+        <v>340500</v>
       </c>
       <c r="M8" t="n">
-        <v>30100</v>
+        <v>313500</v>
       </c>
       <c r="N8" t="n">
-        <v>11.44</v>
+        <v>1.96</v>
       </c>
       <c r="O8" t="n">
-        <v>35138784150</v>
+        <v>49434848000</v>
       </c>
       <c r="P8" t="n">
-        <v>75900</v>
+        <v>635000</v>
       </c>
       <c r="Q8" t="n">
-        <v>15000</v>
+        <v>52600</v>
       </c>
       <c r="R8" t="n">
-        <v>-117000</v>
+        <v>-23000</v>
       </c>
       <c r="S8" t="n">
         <v>0</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>오늘 상승 기대감 속, 전선주 전반의 약세 및 주가 하락세가 관찰됨.</t>
+          <t>가온전선 주가 고평가 논란 속 차익 실현 가능성 언급. 외국인 및 기관 수급 변동성 존재.</t>
         </is>
       </c>
       <c r="U8" t="inlineStr"/>
       <c r="V8" t="n">
-        <v>0.05</v>
+        <v>0.1</v>
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>['전선주', '수급', '하락']</t>
+          <t>['가온전선', '고평가', '외국인']</t>
         </is>
       </c>
       <c r="X8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Y8" t="inlineStr">
         <is>
@@ -1200,77 +1200,77 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>001440</t>
+          <t>000500</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>오름테라퓨틱</t>
+          <t>대한전선</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>26850</v>
+        <v>30050</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>'-28.21%</t>
+          <t>'-4.45%</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>0.01</v>
+        <v>0.48</v>
       </c>
       <c r="E9" t="n">
-        <v>344</v>
+        <v>48</v>
       </c>
       <c r="F9" t="n">
-        <v>213</v>
+        <v>30</v>
       </c>
       <c r="G9" t="n">
-        <v>702</v>
+        <v>81</v>
       </c>
       <c r="H9" t="n">
-        <v>7.09</v>
+        <v>11.92</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J9" t="n">
-        <v>37400</v>
+        <v>31450</v>
       </c>
       <c r="K9" t="n">
-        <v>26450</v>
+        <v>31500</v>
       </c>
       <c r="L9" t="n">
-        <v>27300</v>
+        <v>31550</v>
       </c>
       <c r="M9" t="n">
-        <v>26200</v>
+        <v>30050</v>
       </c>
       <c r="N9" t="n">
-        <v>7.08</v>
+        <v>11.44</v>
       </c>
       <c r="O9" t="n">
-        <v>38457487475</v>
+        <v>40937270775</v>
       </c>
       <c r="P9" t="n">
-        <v>146600</v>
+        <v>75900</v>
       </c>
       <c r="Q9" t="n">
-        <v>26200</v>
+        <v>15000</v>
       </c>
       <c r="R9" t="n">
-        <v>8000</v>
+        <v>-117000</v>
       </c>
       <c r="S9" t="n">
         <v>0</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>하한가 기록 후 반등 시도하나, 임상 결과 및 글로벌 제약사 협상 지연으로 인한 불확실성 지속.</t>
+          <t>대한전선 주가 흐름 둔화, 전선주 수급 불확실성 존재. 원전 및 전력 인프라 투자 영향 가능성 언급.</t>
         </is>
       </c>
       <c r="U9" t="inlineStr"/>
@@ -1279,18 +1279,202 @@
       </c>
       <c r="W9" t="inlineStr">
         <is>
+          <t>['대한전선', '전선주', '원전']</t>
+        </is>
+      </c>
+      <c r="X9" t="n">
+        <v>2</v>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>활성</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>001440</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>한화시스템</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>76300</v>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>'-4.62%</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>-0.1</v>
+      </c>
+      <c r="E10" t="n">
+        <v>76</v>
+      </c>
+      <c r="F10" t="n">
+        <v>51</v>
+      </c>
+      <c r="G10" t="n">
+        <v>299</v>
+      </c>
+      <c r="H10" t="n">
+        <v>10.58</v>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>MarketType.KOSPI</t>
+        </is>
+      </c>
+      <c r="J10" t="n">
+        <v>80000</v>
+      </c>
+      <c r="K10" t="n">
+        <v>82900</v>
+      </c>
+      <c r="L10" t="n">
+        <v>83000</v>
+      </c>
+      <c r="M10" t="n">
+        <v>75900</v>
+      </c>
+      <c r="N10" t="n">
+        <v>10.68</v>
+      </c>
+      <c r="O10" t="n">
+        <v>52004132350</v>
+      </c>
+      <c r="P10" t="n">
+        <v>184000</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>44750</v>
+      </c>
+      <c r="R10" t="n">
+        <v>-260000</v>
+      </c>
+      <c r="S10" t="n">
+        <v>0</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>K-방산, 다층 대드론 시장 개척 가능성 제시. 공매도 및 매물대 돌파 여부 중요. 프리장 매도세 확인.</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr"/>
+      <c r="V10" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>['K-방산', '드론', '공매도']</t>
+        </is>
+      </c>
+      <c r="X10" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>활성</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>272210</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>오름테라퓨틱</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>27550</v>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>'-26.34%</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="E11" t="n">
+        <v>384</v>
+      </c>
+      <c r="F11" t="n">
+        <v>231</v>
+      </c>
+      <c r="G11" t="n">
+        <v>779</v>
+      </c>
+      <c r="H11" t="n">
+        <v>7.09</v>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>MarketType.KOSDAQ</t>
+        </is>
+      </c>
+      <c r="J11" t="n">
+        <v>37400</v>
+      </c>
+      <c r="K11" t="n">
+        <v>26450</v>
+      </c>
+      <c r="L11" t="n">
+        <v>28200</v>
+      </c>
+      <c r="M11" t="n">
+        <v>26200</v>
+      </c>
+      <c r="N11" t="n">
+        <v>7.08</v>
+      </c>
+      <c r="O11" t="n">
+        <v>49955347700</v>
+      </c>
+      <c r="P11" t="n">
+        <v>146600</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>26200</v>
+      </c>
+      <c r="R11" t="n">
+        <v>8000</v>
+      </c>
+      <c r="S11" t="n">
+        <v>0</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>하한가 기록 후 반등 시도하나, 임상 결과 및 글로벌 제약사 협상 지연으로 인한 불확실성 지속.</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr"/>
+      <c r="V11" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
           <t>['임상', '바이오', '하한가']</t>
         </is>
       </c>
-      <c r="X9" t="n">
+      <c r="X11" t="n">
         <v>1</v>
       </c>
-      <c r="Y9" t="inlineStr">
+      <c r="Y11" t="inlineStr">
         <is>
           <t>활성</t>
         </is>
       </c>
-      <c r="Z9" t="inlineStr">
+      <c r="Z11" t="inlineStr">
         <is>
           <t>475830</t>
         </is>

--- a/data/trending_integrated_20260921_09.xlsx
+++ b/data/trending_integrated_20260921_09.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Z11"/>
+  <dimension ref="A1:Z12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -567,24 +567,24 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>22550</v>
+        <v>22650</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>'+16.00%</t>
+          <t>'+16.51%</t>
         </is>
       </c>
       <c r="D2" t="n">
         <v>-0.04</v>
       </c>
       <c r="E2" t="n">
-        <v>44</v>
+        <v>56</v>
       </c>
       <c r="F2" t="n">
-        <v>39</v>
+        <v>47</v>
       </c>
       <c r="G2" t="n">
-        <v>73</v>
+        <v>91</v>
       </c>
       <c r="H2" t="n">
         <v>0.35</v>
@@ -601,7 +601,7 @@
         <v>20200</v>
       </c>
       <c r="L2" t="n">
-        <v>23150</v>
+        <v>23400</v>
       </c>
       <c r="M2" t="n">
         <v>19610</v>
@@ -610,7 +610,7 @@
         <v>0.39</v>
       </c>
       <c r="O2" t="n">
-        <v>77373063160</v>
+        <v>93085250985</v>
       </c>
       <c r="P2" t="n">
         <v>39350</v>
@@ -626,7 +626,7 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>美 타임 선정 '세계 최고 헬스테크 기업' 그룹 선정, 글로벌 경쟁력 부각. 주가 급락 후 반등 시도.</t>
+          <t>美 타임 선정 '세계 최고 헬스테크 기업' 그룹 선정이라는 긍정적 뉴스 기반. 글로벌 빅테크 탐색 및 AI 혁명 언급.</t>
         </is>
       </c>
       <c r="U2" t="inlineStr"/>
@@ -635,7 +635,7 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>['헬스테크', '타임지', '바이오']</t>
+          <t>['헬스테크', '타임지', 'AI']</t>
         </is>
       </c>
       <c r="X2" t="n">
@@ -659,24 +659,24 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>11440</v>
+        <v>11210</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>'+8.75%</t>
+          <t>'+6.56%</t>
         </is>
       </c>
       <c r="D3" t="n">
         <v>0.16</v>
       </c>
       <c r="E3" t="n">
-        <v>44</v>
+        <v>53</v>
       </c>
       <c r="F3" t="n">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="G3" t="n">
-        <v>103</v>
+        <v>110</v>
       </c>
       <c r="H3" t="n">
         <v>18.29</v>
@@ -702,7 +702,7 @@
         <v>18.13</v>
       </c>
       <c r="O3" t="n">
-        <v>132353333595</v>
+        <v>140330912335</v>
       </c>
       <c r="P3" t="n">
         <v>22450</v>
@@ -711,14 +711,14 @@
         <v>1760</v>
       </c>
       <c r="R3" t="n">
-        <v>167000</v>
+        <v>-18000</v>
       </c>
       <c r="S3" t="n">
         <v>0</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>광통신주 및 나스닥 선물 상승 영향, 추격 매수 주의.</t>
+          <t>미국 광통신주 급등 및 나스닥 선물 지수 호조에 따른 기대감. 다만, 섣부른 판단은 금물이라는 신중론도 존재.</t>
         </is>
       </c>
       <c r="U3" t="inlineStr"/>
@@ -727,7 +727,7 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>['광통신', '나스닥', 'RFHIC']</t>
+          <t>['광통신', '나스닥', '흐름']</t>
         </is>
       </c>
       <c r="X3" t="n">
@@ -751,24 +751,24 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>269500</v>
+        <v>270000</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>'+3.26%</t>
+          <t>'+3.45%</t>
         </is>
       </c>
       <c r="D4" t="n">
         <v>-0.02</v>
       </c>
       <c r="E4" t="n">
-        <v>510</v>
+        <v>550</v>
       </c>
       <c r="F4" t="n">
-        <v>338</v>
+        <v>367</v>
       </c>
       <c r="G4" t="n">
-        <v>2144</v>
+        <v>2310</v>
       </c>
       <c r="H4" t="n">
         <v>46.46</v>
@@ -794,7 +794,7 @@
         <v>46.48</v>
       </c>
       <c r="O4" t="n">
-        <v>1402434337250</v>
+        <v>1612027252750</v>
       </c>
       <c r="P4" t="n">
         <v>374500</v>
@@ -803,14 +803,14 @@
         <v>81100</v>
       </c>
       <c r="R4" t="n">
-        <v>1280000</v>
+        <v>2588000</v>
       </c>
       <c r="S4" t="n">
-        <v>0</v>
+        <v>189000</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>AI 감속론 부인, 배당 기대감 속 목표가 27만원 제시. 신한증권 서버 불안정 문제 발생.</t>
+          <t>AI 감속론 우려에도 불구하고 배당 기대감 등으로 상승 출발 전망. 신한증권 시스템 먹통에 대한 불만 제기.</t>
         </is>
       </c>
       <c r="U4" t="inlineStr"/>
@@ -819,7 +819,7 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>['AI', '배당', '목표가']</t>
+          <t>['AI', '배당', '신한증권']</t>
         </is>
       </c>
       <c r="X4" t="n">
@@ -843,24 +843,24 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>30250</v>
+        <v>30200</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>'+2.02%</t>
+          <t>'+1.85%</t>
         </is>
       </c>
       <c r="D5" t="n">
         <v>-0.48</v>
       </c>
       <c r="E5" t="n">
-        <v>88</v>
+        <v>92</v>
       </c>
       <c r="F5" t="n">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="G5" t="n">
-        <v>613</v>
+        <v>654</v>
       </c>
       <c r="H5" t="n">
         <v>16.67</v>
@@ -886,7 +886,7 @@
         <v>17.15</v>
       </c>
       <c r="O5" t="n">
-        <v>3722766750</v>
+        <v>4072297750</v>
       </c>
       <c r="P5" t="n">
         <v>69200</v>
@@ -898,20 +898,20 @@
         <v>-16000</v>
       </c>
       <c r="S5" t="n">
-        <v>0</v>
+        <v>-1000</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>FDA 승인 관련 불확실성 지속, 담관암 임상 결과 및 과거 패턴 반복에 대한 우려 제기. 투자 주의 경고.</t>
+          <t>담관암 NDA 통과 및 FDA 승인 기대감 속, 앞선 패턴과 동일한 설레발 및 속지 말자는 경고. 오름테라퓨틱스 사례 언급.</t>
         </is>
       </c>
       <c r="U5" t="inlineStr"/>
       <c r="V5" t="n">
-        <v>0.1</v>
+        <v>0.3</v>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>['FDA', '승인', '임상']</t>
+          <t>['담관암', 'FDA', 'NDA']</t>
         </is>
       </c>
       <c r="X5" t="n">
@@ -931,83 +931,83 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>SK하이닉스</t>
+          <t>미투온</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1859000</v>
+        <v>4245</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>'+0.11%</t>
+          <t>'+0.59%</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>0.13</v>
+        <v>-0.22</v>
       </c>
       <c r="E6" t="n">
-        <v>586</v>
+        <v>45</v>
       </c>
       <c r="F6" t="n">
-        <v>361</v>
+        <v>29</v>
       </c>
       <c r="G6" t="n">
-        <v>2466</v>
+        <v>96</v>
       </c>
       <c r="H6" t="n">
-        <v>50.23</v>
+        <v>0.33</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J6" t="n">
-        <v>1857000</v>
+        <v>4220</v>
       </c>
       <c r="K6" t="n">
-        <v>1872000</v>
+        <v>4220</v>
       </c>
       <c r="L6" t="n">
-        <v>1888000</v>
+        <v>4415</v>
       </c>
       <c r="M6" t="n">
-        <v>1847000</v>
+        <v>4180</v>
       </c>
       <c r="N6" t="n">
-        <v>50.1</v>
+        <v>0.55</v>
       </c>
       <c r="O6" t="n">
-        <v>1141935987500</v>
+        <v>21304476018</v>
       </c>
       <c r="P6" t="n">
-        <v>2987000</v>
+        <v>6480</v>
       </c>
       <c r="Q6" t="n">
-        <v>333000</v>
+        <v>1738</v>
       </c>
       <c r="R6" t="n">
-        <v>-60000</v>
+        <v>54000</v>
       </c>
       <c r="S6" t="n">
         <v>0</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>HBM 수율 문제에도 불구, 반도체 시장 성장 및 수출 호조 전망. 외인 매수세 유입 및 200만닉스 돌파 기대.</t>
+          <t>미버스 급등에 따른 기대감 및 코인 관련주 동반 상승 분위기. 다만, 거래량 부족 및 힘없는 모습 지적.</t>
         </is>
       </c>
       <c r="U6" t="inlineStr"/>
       <c r="V6" t="n">
-        <v>0.6</v>
+        <v>0.2</v>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>['HBM', '반도체', '수출']</t>
+          <t>['미버스', '코인', '거래량']</t>
         </is>
       </c>
       <c r="X6" t="n">
-        <v>75</v>
+        <v>4</v>
       </c>
       <c r="Y6" t="inlineStr">
         <is>
@@ -1016,90 +1016,90 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>000660</t>
+          <t>201490</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>대한광통신</t>
+          <t>SK하이닉스</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>17790</v>
+        <v>1868000</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>'-2.89%</t>
+          <t>'+0.59%</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>3.29</v>
+        <v>0.13</v>
       </c>
       <c r="E7" t="n">
-        <v>112</v>
+        <v>633</v>
       </c>
       <c r="F7" t="n">
-        <v>83</v>
+        <v>389</v>
       </c>
       <c r="G7" t="n">
-        <v>558</v>
+        <v>2593</v>
       </c>
       <c r="H7" t="n">
-        <v>7.9</v>
+        <v>50.23</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J7" t="n">
-        <v>18320</v>
+        <v>1857000</v>
       </c>
       <c r="K7" t="n">
-        <v>18450</v>
+        <v>1872000</v>
       </c>
       <c r="L7" t="n">
-        <v>18590</v>
+        <v>1888000</v>
       </c>
       <c r="M7" t="n">
-        <v>17590</v>
+        <v>1847000</v>
       </c>
       <c r="N7" t="n">
-        <v>4.61</v>
+        <v>50.1</v>
       </c>
       <c r="O7" t="n">
-        <v>120891809385</v>
+        <v>1265922293000</v>
       </c>
       <c r="P7" t="n">
-        <v>31500</v>
+        <v>2987000</v>
       </c>
       <c r="Q7" t="n">
-        <v>1272</v>
+        <v>333000</v>
       </c>
       <c r="R7" t="n">
-        <v>-762000</v>
+        <v>-78000</v>
       </c>
       <c r="S7" t="n">
-        <v>0</v>
+        <v>55000</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>미국 광통신주 및 나스닥 선물 상승에 따른 긍정적 전망. 기관 매수세 확인 및 연말까지 상승 기대.</t>
+          <t>HBM 수율 문제에도 불구, 반도체 시장 성장 및 수출 호조 전망. 외인 매수세 유입 및 200만닉스 돌파 기대.</t>
         </is>
       </c>
       <c r="U7" t="inlineStr"/>
       <c r="V7" t="n">
-        <v>0.5</v>
+        <v>0.6</v>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>['광통신', '나스닥', '기관']</t>
+          <t>['HBM', '반도체', '수출']</t>
         </is>
       </c>
       <c r="X7" t="n">
-        <v>19</v>
+        <v>75</v>
       </c>
       <c r="Y7" t="inlineStr">
         <is>
@@ -1108,90 +1108,90 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>010170</t>
+          <t>000660</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>가온전선</t>
+          <t>대한광통신</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>313500</v>
+        <v>17620</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>'-4.13%</t>
+          <t>'-3.82%</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>1.66</v>
+        <v>3.29</v>
       </c>
       <c r="E8" t="n">
-        <v>69</v>
+        <v>123</v>
       </c>
       <c r="F8" t="n">
-        <v>50</v>
+        <v>90</v>
       </c>
       <c r="G8" t="n">
-        <v>139</v>
+        <v>592</v>
       </c>
       <c r="H8" t="n">
-        <v>3.62</v>
+        <v>7.9</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J8" t="n">
-        <v>327000</v>
+        <v>18320</v>
       </c>
       <c r="K8" t="n">
-        <v>324000</v>
+        <v>18450</v>
       </c>
       <c r="L8" t="n">
-        <v>340500</v>
+        <v>18590</v>
       </c>
       <c r="M8" t="n">
-        <v>313500</v>
+        <v>17590</v>
       </c>
       <c r="N8" t="n">
-        <v>1.96</v>
+        <v>4.61</v>
       </c>
       <c r="O8" t="n">
-        <v>49434848000</v>
+        <v>130061711280</v>
       </c>
       <c r="P8" t="n">
-        <v>635000</v>
+        <v>31500</v>
       </c>
       <c r="Q8" t="n">
-        <v>52600</v>
+        <v>1272</v>
       </c>
       <c r="R8" t="n">
-        <v>-23000</v>
+        <v>-762000</v>
       </c>
       <c r="S8" t="n">
         <v>0</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>가온전선 주가 고평가 논란 속 차익 실현 가능성 언급. 외국인 및 기관 수급 변동성 존재.</t>
+          <t>미국 광통신 AI주 급등 및 기관 매수세 유입에 따른 연말, 연초까지의 긍정적 전망. 조정장 매수 기회 언급.</t>
         </is>
       </c>
       <c r="U8" t="inlineStr"/>
       <c r="V8" t="n">
-        <v>0.1</v>
+        <v>0.5</v>
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>['가온전선', '고평가', '외국인']</t>
+          <t>['광통신', 'AI', '기관']</t>
         </is>
       </c>
       <c r="X8" t="n">
-        <v>1</v>
+        <v>19</v>
       </c>
       <c r="Y8" t="inlineStr">
         <is>
@@ -1200,7 +1200,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>000500</t>
+          <t>010170</t>
         </is>
       </c>
     </row>
@@ -1211,24 +1211,24 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>30050</v>
+        <v>30100</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>'-4.45%</t>
+          <t>'-4.29%</t>
         </is>
       </c>
       <c r="D9" t="n">
         <v>0.48</v>
       </c>
       <c r="E9" t="n">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="F9" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="G9" t="n">
-        <v>81</v>
+        <v>88</v>
       </c>
       <c r="H9" t="n">
         <v>11.92</v>
@@ -1248,13 +1248,13 @@
         <v>31550</v>
       </c>
       <c r="M9" t="n">
-        <v>30050</v>
+        <v>30000</v>
       </c>
       <c r="N9" t="n">
         <v>11.44</v>
       </c>
       <c r="O9" t="n">
-        <v>40937270775</v>
+        <v>44841203075</v>
       </c>
       <c r="P9" t="n">
         <v>75900</v>
@@ -1263,14 +1263,14 @@
         <v>15000</v>
       </c>
       <c r="R9" t="n">
-        <v>-117000</v>
+        <v>-166000</v>
       </c>
       <c r="S9" t="n">
-        <v>0</v>
+        <v>-8000</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>대한전선 주가 흐름 둔화, 전선주 수급 불확실성 존재. 원전 및 전력 인프라 투자 영향 가능성 언급.</t>
+          <t>오늘의 주종목으로 기대를 모았으나 금일 하락 마감. 원전 및 전력 인프라 관련 파급력 언급.</t>
         </is>
       </c>
       <c r="U9" t="inlineStr"/>
@@ -1299,31 +1299,31 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>한화시스템</t>
+          <t>가온전선</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>76300</v>
+        <v>312500</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>'-4.62%</t>
+          <t>'-4.43%</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>-0.1</v>
+        <v>1.66</v>
       </c>
       <c r="E10" t="n">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="F10" t="n">
-        <v>51</v>
+        <v>55</v>
       </c>
       <c r="G10" t="n">
-        <v>299</v>
+        <v>157</v>
       </c>
       <c r="H10" t="n">
-        <v>10.58</v>
+        <v>3.62</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
@@ -1331,38 +1331,38 @@
         </is>
       </c>
       <c r="J10" t="n">
-        <v>80000</v>
+        <v>327000</v>
       </c>
       <c r="K10" t="n">
-        <v>82900</v>
+        <v>324000</v>
       </c>
       <c r="L10" t="n">
-        <v>83000</v>
+        <v>340500</v>
       </c>
       <c r="M10" t="n">
-        <v>75900</v>
+        <v>312500</v>
       </c>
       <c r="N10" t="n">
-        <v>10.68</v>
+        <v>1.96</v>
       </c>
       <c r="O10" t="n">
-        <v>52004132350</v>
+        <v>52999216250</v>
       </c>
       <c r="P10" t="n">
-        <v>184000</v>
+        <v>635000</v>
       </c>
       <c r="Q10" t="n">
-        <v>44750</v>
+        <v>52600</v>
       </c>
       <c r="R10" t="n">
-        <v>-260000</v>
+        <v>-24000</v>
       </c>
       <c r="S10" t="n">
-        <v>0</v>
+        <v>-2000</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>K-방산, 다층 대드론 시장 개척 가능성 제시. 공매도 및 매물대 돌파 여부 중요. 프리장 매도세 확인.</t>
+          <t>회장님 따님 수익 언급 및 40만원 돌파 전망. 외국인 수급 및 최고가 갱신 기대와 함께 하락 및 고평가 논란 존재.</t>
         </is>
       </c>
       <c r="U10" t="inlineStr"/>
@@ -1371,7 +1371,7 @@
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>['K-방산', '드론', '공매도']</t>
+          <t>['가온전선', '외국인', '고평가']</t>
         </is>
       </c>
       <c r="X10" t="n">
@@ -1384,86 +1384,86 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>272210</t>
+          <t>000500</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>오름테라퓨틱</t>
+          <t>한화시스템</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>27550</v>
+        <v>75500</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>'-26.34%</t>
+          <t>'-5.62%</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>0.01</v>
+        <v>-0.1</v>
       </c>
       <c r="E11" t="n">
-        <v>384</v>
+        <v>93</v>
       </c>
       <c r="F11" t="n">
-        <v>231</v>
+        <v>59</v>
       </c>
       <c r="G11" t="n">
-        <v>779</v>
+        <v>382</v>
       </c>
       <c r="H11" t="n">
-        <v>7.09</v>
+        <v>10.58</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J11" t="n">
-        <v>37400</v>
+        <v>80000</v>
       </c>
       <c r="K11" t="n">
-        <v>26450</v>
+        <v>82900</v>
       </c>
       <c r="L11" t="n">
-        <v>28200</v>
+        <v>83000</v>
       </c>
       <c r="M11" t="n">
-        <v>26200</v>
+        <v>75400</v>
       </c>
       <c r="N11" t="n">
-        <v>7.08</v>
+        <v>10.68</v>
       </c>
       <c r="O11" t="n">
-        <v>49955347700</v>
+        <v>59713052550</v>
       </c>
       <c r="P11" t="n">
-        <v>146600</v>
+        <v>184000</v>
       </c>
       <c r="Q11" t="n">
-        <v>26200</v>
+        <v>44750</v>
       </c>
       <c r="R11" t="n">
-        <v>8000</v>
+        <v>-324000</v>
       </c>
       <c r="S11" t="n">
-        <v>0</v>
+        <v>-60000</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>하한가 기록 후 반등 시도하나, 임상 결과 및 글로벌 제약사 협상 지연으로 인한 불확실성 지속.</t>
+          <t>K-방산의 다층 대드론 시장 진출 가능성 및 긍정적 뉴스에 따른 기대감. 공매도 세력 규탄 및 10만원대 목표 제시.</t>
         </is>
       </c>
       <c r="U11" t="inlineStr"/>
       <c r="V11" t="n">
-        <v>0.1</v>
+        <v>0.4</v>
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>['임상', '바이오', '하한가']</t>
+          <t>['K-방산', '드론', '공매도']</t>
         </is>
       </c>
       <c r="X11" t="n">
@@ -1475,6 +1475,98 @@
         </is>
       </c>
       <c r="Z11" t="inlineStr">
+        <is>
+          <t>272210</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>오름테라퓨틱</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>26700</v>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>'-28.61%</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="E12" t="n">
+        <v>425</v>
+      </c>
+      <c r="F12" t="n">
+        <v>247</v>
+      </c>
+      <c r="G12" t="n">
+        <v>867</v>
+      </c>
+      <c r="H12" t="n">
+        <v>7.09</v>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>MarketType.KOSDAQ</t>
+        </is>
+      </c>
+      <c r="J12" t="n">
+        <v>37400</v>
+      </c>
+      <c r="K12" t="n">
+        <v>26450</v>
+      </c>
+      <c r="L12" t="n">
+        <v>28200</v>
+      </c>
+      <c r="M12" t="n">
+        <v>26200</v>
+      </c>
+      <c r="N12" t="n">
+        <v>7.08</v>
+      </c>
+      <c r="O12" t="n">
+        <v>55639282975</v>
+      </c>
+      <c r="P12" t="n">
+        <v>146600</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>26200</v>
+      </c>
+      <c r="R12" t="n">
+        <v>8000</v>
+      </c>
+      <c r="S12" t="n">
+        <v>42000</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>하한가 이후 반등 시도했으나, 임상 결과 및 바이오 투기 심리에 대한 부정적 전망. 착한 개미들의 손실 우려.</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr"/>
+      <c r="V12" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>['임상', '바이오', '하한가']</t>
+        </is>
+      </c>
+      <c r="X12" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>활성</t>
+        </is>
+      </c>
+      <c r="Z12" t="inlineStr">
         <is>
           <t>475830</t>
         </is>
